--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2019_T4_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2019_T4_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>79</t>
+    <t>73</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>4.791</t>
-  </si>
-  <si>
-    <t>(3.504)</t>
-  </si>
-  <si>
-    <t>7.519</t>
-  </si>
-  <si>
-    <t>(0.913)</t>
-  </si>
-  <si>
-    <t>9.164</t>
-  </si>
-  <si>
-    <t>(4.145)</t>
-  </si>
-  <si>
-    <t>21.523</t>
-  </si>
-  <si>
-    <t>(7.376)</t>
-  </si>
-  <si>
-    <t>1.291</t>
-  </si>
-  <si>
-    <t>(0.140)</t>
-  </si>
-  <si>
-    <t>8.886</t>
-  </si>
-  <si>
-    <t>(1.060)</t>
-  </si>
-  <si>
-    <t>5.741</t>
-  </si>
-  <si>
-    <t>(1.434)</t>
-  </si>
-  <si>
-    <t>0.536</t>
-  </si>
-  <si>
-    <t>(0.107)</t>
-  </si>
-  <si>
-    <t>29.561</t>
-  </si>
-  <si>
-    <t>(14.051)</t>
-  </si>
-  <si>
-    <t>14.567</t>
-  </si>
-  <si>
-    <t>(4.432)</t>
+    <t>1.365</t>
+  </si>
+  <si>
+    <t>(0.171)</t>
+  </si>
+  <si>
+    <t>8.096</t>
+  </si>
+  <si>
+    <t>(0.957)</t>
+  </si>
+  <si>
+    <t>3.684</t>
+  </si>
+  <si>
+    <t>(0.747)</t>
+  </si>
+  <si>
+    <t>10.806</t>
+  </si>
+  <si>
+    <t>(1.604)</t>
+  </si>
+  <si>
+    <t>1.397</t>
+  </si>
+  <si>
+    <t>(0.144)</t>
+  </si>
+  <si>
+    <t>9.616</t>
+  </si>
+  <si>
+    <t>(1.105)</t>
+  </si>
+  <si>
+    <t>3.794</t>
+  </si>
+  <si>
+    <t>(0.929)</t>
+  </si>
+  <si>
+    <t>0.566</t>
+  </si>
+  <si>
+    <t>(0.114)</t>
+  </si>
+  <si>
+    <t>12.383</t>
+  </si>
+  <si>
+    <t>(1.661)</t>
+  </si>
+  <si>
+    <t>9.387</t>
+  </si>
+  <si>
+    <t>(1.623)</t>
   </si>
   <si>
     <t>37</t>
@@ -198,7 +198,7 @@
     <t>(4.551)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-3.365</t>
-  </si>
-  <si>
-    <t>0.778</t>
-  </si>
-  <si>
-    <t>-0.159</t>
-  </si>
-  <si>
-    <t>-5.126</t>
-  </si>
-  <si>
-    <t>0.197</t>
-  </si>
-  <si>
-    <t>0.654</t>
-  </si>
-  <si>
-    <t>-1.776</t>
-  </si>
-  <si>
-    <t>-0.024</t>
-  </si>
-  <si>
-    <t>-12.274</t>
-  </si>
-  <si>
-    <t>1.658</t>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>0.201</t>
+  </si>
+  <si>
+    <t>5.321***</t>
+  </si>
+  <si>
+    <t>5.590*</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>-0.076</t>
+  </si>
+  <si>
+    <t>0.171</t>
+  </si>
+  <si>
+    <t>-0.053</t>
+  </si>
+  <si>
+    <t>4.904</t>
+  </si>
+  <si>
+    <t>6.838*</t>
   </si>
 </sst>
 </file>
